--- a/tests/fixtures/expected/touren_tak.xlsx
+++ b/tests/fixtures/expected/touren_tak.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[dates]2026-05-10 00:00:00 bis 2026-05-10 23:59:59</t>
+          <t>[dates]2026-05-10 00:00:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[dates]2026-07-18 00:00:00 bis 2026-07-20 23:59:59</t>
+          <t>[dates]2026-07-18 00:00:00 bis 2026-07-20 00:00:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
